--- a/information_request_forms/042_iv_pricing_information_request--information_request_forms.xlsx
+++ b/information_request_forms/042_iv_pricing_information_request--information_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1133,8 +1133,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'iv_drips'}</t>
+          <t>iv_drips</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'IV Drips'}</t>
+          <t>IV Drips</t>
         </is>
       </c>
     </row>
@@ -1179,12 +1179,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'iv_infusions'}</t>
+          <t>iv_infusions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'IV Infusions'}</t>
+          <t>IV Infusions</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'iv_pushes'}</t>
+          <t>iv_pushes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'IV Pushes'}</t>
+          <t>IV Pushes</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'1st'}</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': '1st'}</t>
+          <t>1st</t>
         </is>
       </c>
     </row>
@@ -1264,12 +1264,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'2nd'}</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': '2nd'}</t>
+          <t>2nd</t>
         </is>
       </c>
     </row>
@@ -1281,12 +1281,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'3rd'}</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': '3rd'}</t>
+          <t>3rd</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'not_scheduled'}</t>
+          <t>not_scheduled</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Not Scheduled'}</t>
+          <t>Not Scheduled</t>
         </is>
       </c>
     </row>
@@ -1315,12 +1315,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'scheduled'}</t>
+          <t>scheduled</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Scheduled'}</t>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
